--- a/datatables/datas/节点定义表.xlsx
+++ b/datatables/datas/节点定义表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
   <si>
     <t>##var</t>
   </si>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t>动作</t>
-  </si>
-  <si>
-    <t>GameModule</t>
   </si>
   <si>
     <t>游戏模块</t>
@@ -1466,7 +1463,7 @@
         <v>26</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="8"/>
       <c r="H5" s="9"/>

--- a/datatables/datas/节点定义表.xlsx
+++ b/datatables/datas/节点定义表.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -53,6 +53,9 @@
     <t>pin3</t>
   </si>
   <si>
+    <t>description</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -101,13 +104,55 @@
     <t>引脚3-名称</t>
   </si>
   <si>
-    <t>进入</t>
+    <t>描述</t>
+  </si>
+  <si>
+    <t>进入模块</t>
   </si>
   <si>
     <t>动作</t>
   </si>
   <si>
     <t>游戏模块</t>
+  </si>
+  <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>进入游戏模块，会自动寻路</t>
+  </si>
+  <si>
+    <t>进入副本</t>
+  </si>
+  <si>
+    <t>游戏副本</t>
+  </si>
+  <si>
+    <t>副本</t>
+  </si>
+  <si>
+    <t>进入游戏副本，会自动寻路</t>
+  </si>
+  <si>
+    <t>触发（自动）</t>
+  </si>
+  <si>
+    <t>自动游戏按钮</t>
+  </si>
+  <si>
+    <t>按钮</t>
+  </si>
+  <si>
+    <t>点击游戏按钮，会尝试自动判断当前模块哪个按钮是对应的。</t>
+  </si>
+  <si>
+    <t>触发</t>
+  </si>
+  <si>
+    <t>游戏按钮</t>
+  </si>
+  <si>
+    <t>点击游戏按钮，会自动寻路</t>
   </si>
 </sst>
 </file>
@@ -778,14 +823,14 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1320,8 +1365,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7"/>
   <cols>
     <col min="1" max="1" width="9" style="3"/>
     <col min="2" max="2" width="5" style="3" customWidth="1"/>
@@ -1329,12 +1374,13 @@
     <col min="4" max="4" width="22.0181818181818" style="3" customWidth="1"/>
     <col min="5" max="5" width="14.3272727272727" style="3" customWidth="1"/>
     <col min="6" max="12" width="11.9090909090909" style="3" customWidth="1"/>
-    <col min="13" max="16351" width="9.13636363636364" style="3" customWidth="1"/>
-    <col min="16352" max="16352" width="9.13636363636364" style="3"/>
-    <col min="16353" max="16384" width="9" style="3"/>
+    <col min="13" max="13" width="54.6090909090909" style="3" customWidth="1"/>
+    <col min="14" max="16352" width="9.13636363636364" style="3" customWidth="1"/>
+    <col min="16353" max="16353" width="9.13636363636364" style="3"/>
+    <col min="16354" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1363,40 +1409,46 @@
         <v>7</v>
       </c>
       <c r="L1" s="6"/>
+      <c r="M1" s="5" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:12">
+    <row r="2" s="1" customFormat="1" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J2" s="6"/>
       <c r="K2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="6"/>
+      <c r="M2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="6"/>
     </row>
-    <row r="3" s="2" customFormat="1" ht="14.5" spans="1:12">
+    <row r="3" s="2" customFormat="1" ht="14.5" spans="1:13">
       <c r="A3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -1409,68 +1461,156 @@
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
+      <c r="M3" s="5"/>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:12">
+    <row r="4" s="1" customFormat="1" spans="1:13">
       <c r="A4" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:13">
       <c r="A5" s="7"/>
       <c r="B5" s="8">
         <v>1001</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>29</v>
       </c>
       <c r="G5" s="8"/>
-      <c r="H5" s="9"/>
+      <c r="H5" s="8"/>
       <c r="I5" s="8"/>
-      <c r="J5" s="9"/>
+      <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-      <c r="L5" s="9"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="7"/>
+      <c r="B6" s="8">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="7"/>
+      <c r="B7" s="8">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="9" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="7"/>
+      <c r="B8" s="8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="9" t="s">
+        <v>41</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="12">

--- a/datatables/datas/节点定义表.xlsx
+++ b/datatables/datas/节点定义表.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowHeight="17230"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="节点定义表" sheetId="1" r:id="rId1"/>
@@ -134,7 +134,7 @@
     <t>进入游戏副本，会自动寻路</t>
   </si>
   <si>
-    <t>触发（自动）</t>
+    <t>触发（易用版）</t>
   </si>
   <si>
     <t>自动游戏按钮</t>
